--- a/public/post/drafts/season-prediction/ladies_breakthrough-predictions-2025-final.xlsx
+++ b/public/post/drafts/season-prediction/ladies_breakthrough-predictions-2025-final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -52,7 +52,16 @@
     <t xml:space="preserve">Prev_Pelo</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Distance</t>
+    <t xml:space="preserve">Kristine Stavås Skistad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
   </si>
   <si>
     <t xml:space="preserve">Johanna Matintalo</t>
@@ -61,28 +70,61 @@
     <t xml:space="preserve">Finland</t>
   </si>
   <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristine Stavås Skistad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norway</t>
-  </si>
-  <si>
     <t xml:space="preserve">Very Low</t>
   </si>
   <si>
     <t xml:space="preserve">High</t>
   </si>
   <si>
+    <t xml:space="preserve">Johanna Hagström</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mathilde Myhrvold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moa Lundgren</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coletta Rydzek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margrethe Bergane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmi Joensuu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laura Gimmler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maja Dahlqvist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Kjersti Kalvå</t>
+  </si>
+  <si>
     <t xml:space="preserve">Astrid Øyre Slind</t>
   </si>
   <si>
-    <t xml:space="preserve">Margrethe Bergane</t>
+    <t xml:space="preserve">Moa Ilar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jasmin Kähärä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophia Laukli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
   </si>
   <si>
     <t xml:space="preserve">Teresa Stadlober</t>
@@ -91,184 +133,142 @@
     <t xml:space="preserve">Austria</t>
   </si>
   <si>
-    <t xml:space="preserve">Kristin Austgulen Fosnæs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jasmi Joensuu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laura Gimmler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Lundgren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sweden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moa Ilar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathilde Myhrvold</t>
+    <t xml:space="preserve">Katerina Janatova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Czechia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desiree Steiner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Switzerland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia Kern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delphine Claudel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lotta Udnes Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patricijia Eiduka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latvia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alina Meier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flora Dolci</t>
   </si>
   <si>
     <t xml:space="preserve">Katherine Sauerbrey</t>
   </si>
   <si>
-    <t xml:space="preserve">Anne Kjersti Kalvå</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Hagström</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coletta Rydzek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sophia Laukli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katerina Janatova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Czechia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Novie McCabe</t>
   </si>
   <si>
-    <t xml:space="preserve">Lotta Udnes Weng</t>
+    <t xml:space="preserve">Nicole Monsorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anja Weber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pia Fink</t>
   </si>
   <si>
     <t xml:space="preserve">Nadja Kälin</t>
   </si>
   <si>
-    <t xml:space="preserve">Switzerland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pia Fink</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desiree Steiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maja Dahlqvist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anja Weber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flora Dolci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patricijia Eiduka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Latvia</t>
+    <t xml:space="preserve">Lena Quintin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samantha Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tereza Beranova</t>
   </si>
   <si>
     <t xml:space="preserve">Lisa Lohmann</t>
   </si>
   <si>
-    <t xml:space="preserve">Jasmin Kähärä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Delphine Claudel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Caterina Ganz</t>
   </si>
   <si>
-    <t xml:space="preserve">Italy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alina Meier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicole Monsorno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samantha Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julia Kern</t>
-  </si>
-  <si>
     <t xml:space="preserve">Melissa Gal</t>
   </si>
   <si>
+    <t xml:space="preserve">Lena Keck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofie Krehl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbora Antosova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katri Lylynperä</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiia Olkkonen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juliette Ducordeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaidy Kaasiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liliane Gagnon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francesca Franchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lea Fischer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonjaa Schmidt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sofia Henriksson</t>
   </si>
   <si>
-    <t xml:space="preserve">Lena Keck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katri Lylynperä</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lena Quintin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofie Krehl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barbora Antosova</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juliette Ducordeau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesca Franchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaidy Kaasiku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tereza Beranova</t>
+    <t xml:space="preserve">Izabela Marcisz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poland</t>
   </si>
   <si>
     <t xml:space="preserve">Anna Comarella</t>
   </si>
   <si>
-    <t xml:space="preserve">Liliane Gagnon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada</t>
+    <t xml:space="preserve">Keidy Kaasiku</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vilma Ryytty</t>
   </si>
   <si>
     <t xml:space="preserve">Kathrine Stewart-Jones</t>
   </si>
   <si>
-    <t xml:space="preserve">Sonjaa Schmidt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiia Olkkonen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izabela Marcisz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keidy Kaasiku</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lea Fischer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vilma Ryytty</t>
+    <t xml:space="preserve">Lisa Ingesson</t>
   </si>
   <si>
     <t xml:space="preserve">Anja Mandeljc</t>
@@ -277,9 +277,6 @@
     <t xml:space="preserve">Slovenia</t>
   </si>
   <si>
-    <t xml:space="preserve">Lisa Ingesson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Amelia Wells</t>
   </si>
   <si>
@@ -295,18 +292,18 @@
     <t xml:space="preserve">Anna Melnik</t>
   </si>
   <si>
+    <t xml:space="preserve">Darya Ryazhko</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kseniya Shalygina</t>
   </si>
   <si>
+    <t xml:space="preserve">Nadezhda Stepashkina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kitija Auzina</t>
   </si>
   <si>
-    <t xml:space="preserve">Darya Ryazhko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nadezhda Stepashkina</t>
-  </si>
-  <si>
     <t xml:space="preserve">Age_mean</t>
   </si>
   <si>
@@ -319,16 +316,13 @@
     <t xml:space="preserve">Prev_Pelo_mean</t>
   </si>
   <si>
-    <t xml:space="preserve">Prev_Distance_mean</t>
-  </si>
-  <si>
     <t xml:space="preserve">Predictors_Used</t>
   </si>
   <si>
     <t xml:space="preserve">Model_ROC</t>
   </si>
   <si>
-    <t xml:space="preserve">Age, Prev_Pct_of_Max_Points, Prev_Distance_F, Prev_Pelo, Prev_Distance</t>
+    <t xml:space="preserve">Age, Prev_Pct_of_Max_Points, Prev_Distance_F, Prev_Pelo</t>
   </si>
 </sst>
 </file>
@@ -694,131 +688,119 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.309057642152121</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.285230769230769</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.152832489823864</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.214769230769231</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" t="n">
-        <v>27.2635181382615</v>
+        <v>25.09787816564</v>
       </c>
       <c r="J2" t="n">
-        <v>0.226382978723404</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1326.28779016586</v>
+        <v>1284.62144934536</v>
       </c>
       <c r="L2" t="n">
-        <v>1599.42130718551</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1560.61026383801</v>
+        <v>1694.59171167798</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
       <c r="C3" t="n">
-        <v>0.348</v>
+        <v>0.285230769230769</v>
       </c>
       <c r="D3" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0941943024569414</v>
+        <v>0.0820971783419632</v>
       </c>
       <c r="F3" t="n">
-        <v>0.152</v>
+        <v>0.214769230769231</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>25.09787816564</v>
+        <v>27.2635181382615</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.226382978723404</v>
       </c>
       <c r="K3" t="n">
-        <v>1284.62144934536</v>
+        <v>1326.28779016586</v>
       </c>
       <c r="L3" t="n">
-        <v>1694.59171167798</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1277.41185579811</v>
+        <v>1599.42130718551</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" t="n">
-        <v>0.272923076923077</v>
+        <v>0.215692307692308</v>
       </c>
       <c r="D4" t="n">
-        <v>0.272923076923077</v>
+        <v>0.283728813559322</v>
       </c>
       <c r="E4" t="n">
-        <v>0.055462319454971</v>
+        <v>0.0772735285920871</v>
       </c>
       <c r="F4" t="n">
-        <v>0.227076923076923</v>
+        <v>0.284307692307692</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>36.1013004791239</v>
+        <v>25.9712525667351</v>
       </c>
       <c r="J4" t="n">
-        <v>0.280425531914894</v>
+        <v>0.356170212765957</v>
       </c>
       <c r="K4" t="n">
-        <v>1461.70938802762</v>
+        <v>1219.94370361346</v>
       </c>
       <c r="L4" t="n">
-        <v>1641.87864584209</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1658.79967753437</v>
+        <v>1565.126102812</v>
       </c>
     </row>
     <row r="5">
@@ -826,40 +808,37 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>0.295076923076923</v>
+        <v>0.287692307692308</v>
       </c>
       <c r="D5" t="n">
-        <v>0.295076923076923</v>
+        <v>0.287692307692308</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0497219686482845</v>
+        <v>0.0494581831978391</v>
       </c>
       <c r="F5" t="n">
-        <v>0.204923076923077</v>
+        <v>0.212307692307692</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I5" t="n">
-        <v>22.7296372347707</v>
+        <v>25.6646132785763</v>
       </c>
       <c r="J5" t="n">
-        <v>0.178723404255319</v>
+        <v>0.260851063829787</v>
       </c>
       <c r="K5" t="n">
-        <v>1413.20606780157</v>
+        <v>1297.49166797301</v>
       </c>
       <c r="L5" t="n">
-        <v>1494.76039907806</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1514.51963648557</v>
+        <v>1528.52052790386</v>
       </c>
     </row>
     <row r="6">
@@ -867,81 +846,75 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>0.361538461538462</v>
+        <v>0.270153846153846</v>
       </c>
       <c r="D6" t="n">
-        <v>0.469</v>
+        <v>0.270153846153846</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0435255958659605</v>
+        <v>0.0403087807554305</v>
       </c>
       <c r="F6" t="n">
-        <v>0.138461538461538</v>
+        <v>0.229846153846154</v>
       </c>
       <c r="G6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>31.1211498973306</v>
+        <v>25.9219712525667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.398297872340426</v>
+        <v>0.223829787234043</v>
       </c>
       <c r="K6" t="n">
-        <v>1521.55558406808</v>
+        <v>1330.98633357921</v>
       </c>
       <c r="L6" t="n">
-        <v>1592.28503737702</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1681.83564607681</v>
+        <v>1516.45692035555</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
       <c r="C7" t="n">
-        <v>0.302153846153846</v>
+        <v>0.285846153846154</v>
       </c>
       <c r="D7" t="n">
-        <v>0.302153846153846</v>
+        <v>0.285846153846154</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0389706695295193</v>
+        <v>0.0399185586450744</v>
       </c>
       <c r="F7" t="n">
-        <v>0.197846153846154</v>
+        <v>0.214153846153846</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>23.7946611909651</v>
+        <v>26.776180698152</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.346382978723404</v>
       </c>
       <c r="K7" t="n">
-        <v>1372.04780913445</v>
+        <v>1286.43643578636</v>
       </c>
       <c r="L7" t="n">
-        <v>1456.86494840807</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1459.47454667952</v>
+        <v>1524.5464394304</v>
       </c>
     </row>
     <row r="8">
@@ -949,40 +922,37 @@
         <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>0.266769230769231</v>
+        <v>0.295076923076923</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3025</v>
+        <v>0.295076923076923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0376501680348877</v>
+        <v>0.0389004480828249</v>
       </c>
       <c r="F8" t="n">
-        <v>0.233230769230769</v>
+        <v>0.204923076923077</v>
       </c>
       <c r="G8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" t="n">
-        <v>27.8576317590691</v>
+        <v>22.7296372347707</v>
       </c>
       <c r="J8" t="n">
-        <v>0.28936170212766</v>
+        <v>0.178723404255319</v>
       </c>
       <c r="K8" t="n">
-        <v>1307.25296945496</v>
+        <v>1413.20606780157</v>
       </c>
       <c r="L8" t="n">
-        <v>1532.66343795495</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1421.52116375763</v>
+        <v>1494.76039907806</v>
       </c>
     </row>
     <row r="9">
@@ -990,335 +960,311 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>0.280923076923077</v>
+        <v>0.266769230769231</v>
       </c>
       <c r="D9" t="n">
-        <v>0.416949152542373</v>
+        <v>0.3025</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0362973944765955</v>
+        <v>0.0384637964211462</v>
       </c>
       <c r="F9" t="n">
-        <v>0.219076923076923</v>
+        <v>0.233230769230769</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>30.280629705681</v>
+        <v>27.8576317590691</v>
       </c>
       <c r="J9" t="n">
-        <v>0.523404255319149</v>
+        <v>0.28936170212766</v>
       </c>
       <c r="K9" t="n">
-        <v>1286.46768869959</v>
+        <v>1307.25296945496</v>
       </c>
       <c r="L9" t="n">
-        <v>1565.09720728919</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1438.82819355347</v>
+        <v>1532.66343795495</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>0.270153846153846</v>
+        <v>0.280923076923077</v>
       </c>
       <c r="D10" t="n">
-        <v>0.270153846153846</v>
+        <v>0.416949152542373</v>
       </c>
       <c r="E10" t="n">
-        <v>0.035030343237058</v>
+        <v>0.0350861986842536</v>
       </c>
       <c r="F10" t="n">
-        <v>0.229846153846154</v>
+        <v>0.219076923076923</v>
       </c>
       <c r="G10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>25.9219712525667</v>
+        <v>30.280629705681</v>
       </c>
       <c r="J10" t="n">
-        <v>0.223829787234043</v>
+        <v>0.523404255319149</v>
       </c>
       <c r="K10" t="n">
-        <v>1330.98633357921</v>
+        <v>1286.46768869959</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.45692035555</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1412.35086333036</v>
+        <v>1565.09720728919</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>0.351076923076923</v>
+        <v>0.315076923076923</v>
       </c>
       <c r="D11" t="n">
-        <v>0.351076923076923</v>
+        <v>0.436610169491525</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0340796936041556</v>
+        <v>0.0342370757343804</v>
       </c>
       <c r="F11" t="n">
-        <v>0.148923076923077</v>
+        <v>0.184923076923077</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>26.6967830253251</v>
+        <v>29.9219712525667</v>
       </c>
       <c r="J11" t="n">
-        <v>0.373617021276596</v>
+        <v>0.548085106382979</v>
       </c>
       <c r="K11" t="n">
-        <v>1434.10578308781</v>
+        <v>1403.82961319924</v>
       </c>
       <c r="L11" t="n">
-        <v>1542.40212691082</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1531.14460704945</v>
+        <v>1589.34409284569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>0.287692307692308</v>
+        <v>0.235076923076923</v>
       </c>
       <c r="D12" t="n">
-        <v>0.287692307692308</v>
+        <v>0.386440677966102</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0287283225357785</v>
+        <v>0.0327504434125808</v>
       </c>
       <c r="F12" t="n">
-        <v>0.212307692307692</v>
+        <v>0.264923076923077</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" t="n">
-        <v>25.6646132785763</v>
+        <v>31.7809719370294</v>
       </c>
       <c r="J12" t="n">
-        <v>0.260851063829787</v>
+        <v>0.485106382978723</v>
       </c>
       <c r="K12" t="n">
-        <v>1297.49166797301</v>
+        <v>1548.59048418489</v>
       </c>
       <c r="L12" t="n">
-        <v>1528.52052790386</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1339.48375843785</v>
+        <v>1634.48001208269</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>0.174461538461538</v>
+        <v>0.272923076923077</v>
       </c>
       <c r="D13" t="n">
-        <v>0.174461538461538</v>
+        <v>0.272923076923077</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0283908320990743</v>
+        <v>0.0326687364074019</v>
       </c>
       <c r="F13" t="n">
-        <v>0.325538461538462</v>
+        <v>0.227076923076923</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" t="n">
-        <v>26.8665297741273</v>
+        <v>36.1013004791239</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.280425531914894</v>
       </c>
       <c r="K13" t="n">
-        <v>1309.11136166604</v>
+        <v>1461.70938802762</v>
       </c>
       <c r="L13" t="n">
-        <v>1423.58983614881</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1427.63585888296</v>
+        <v>1641.87864584209</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>0.235076923076923</v>
+        <v>0.351076923076923</v>
       </c>
       <c r="D14" t="n">
-        <v>0.386440677966102</v>
+        <v>0.351076923076923</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0282999097454427</v>
+        <v>0.0326268347146005</v>
       </c>
       <c r="F14" t="n">
-        <v>0.264923076923077</v>
+        <v>0.148923076923077</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>31.7809719370294</v>
+        <v>26.6967830253251</v>
       </c>
       <c r="J14" t="n">
-        <v>0.485106382978723</v>
+        <v>0.373617021276596</v>
       </c>
       <c r="K14" t="n">
-        <v>1548.59048418489</v>
+        <v>1434.10578308781</v>
       </c>
       <c r="L14" t="n">
-        <v>1634.48001208269</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1634.67467326321</v>
+        <v>1542.40212691082</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.215692307692308</v>
+        <v>0.120615384615385</v>
       </c>
       <c r="D15" t="n">
-        <v>0.283728813559322</v>
+        <v>0.154</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0271928754688629</v>
+        <v>0.0320892766622408</v>
       </c>
       <c r="F15" t="n">
-        <v>0.284307692307692</v>
+        <v>0.379384615384615</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>25.9712525667351</v>
+        <v>23.854893908282</v>
       </c>
       <c r="J15" t="n">
-        <v>0.356170212765957</v>
+        <v>0.188936170212766</v>
       </c>
       <c r="K15" t="n">
-        <v>1219.94370361346</v>
+        <v>1276.18788638353</v>
       </c>
       <c r="L15" t="n">
-        <v>1565.126102812</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1233.39151557325</v>
+        <v>1456.32761576326</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>0.285846153846154</v>
+        <v>0.302153846153846</v>
       </c>
       <c r="D16" t="n">
-        <v>0.285846153846154</v>
+        <v>0.302153846153846</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0245110660192724</v>
+        <v>0.0302600995835996</v>
       </c>
       <c r="F16" t="n">
-        <v>0.214153846153846</v>
+        <v>0.197846153846154</v>
       </c>
       <c r="G16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>26.776180698152</v>
+        <v>23.7946611909651</v>
       </c>
       <c r="J16" t="n">
-        <v>0.346382978723404</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1286.43643578636</v>
+        <v>1372.04780913445</v>
       </c>
       <c r="L16" t="n">
-        <v>1524.5464394304</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1341.18126912984</v>
+        <v>1456.86494840807</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
         <v>0.290153846153846</v>
@@ -1327,16 +1273,16 @@
         <v>0.290153846153846</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0238470658469727</v>
+        <v>0.0281313602392545</v>
       </c>
       <c r="F17" t="n">
         <v>0.209846153846154</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
         <v>23.772758384668</v>
@@ -1350,131 +1296,119 @@
       <c r="L17" t="n">
         <v>1488.6187678426</v>
       </c>
-      <c r="M17" t="n">
-        <v>1507.77596335782</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" t="n">
-        <v>0.355076923076923</v>
+        <v>0.361538461538462</v>
       </c>
       <c r="D18" t="n">
-        <v>0.355076923076923</v>
+        <v>0.469</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0218808349268492</v>
+        <v>0.0262122218663671</v>
       </c>
       <c r="F18" t="n">
-        <v>0.144923076923077</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="G18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>27.0116358658453</v>
+        <v>31.1211498973306</v>
       </c>
       <c r="J18" t="n">
-        <v>0.397872340425532</v>
+        <v>0.398297872340426</v>
       </c>
       <c r="K18" t="n">
-        <v>1399.33010741962</v>
+        <v>1521.55558406808</v>
       </c>
       <c r="L18" t="n">
-        <v>1509.73901053658</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1473.95310727914</v>
+        <v>1592.28503737702</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0907692307692308</v>
+        <v>0.355076923076923</v>
       </c>
       <c r="D19" t="n">
-        <v>0.112</v>
+        <v>0.355076923076923</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0214871847077416</v>
+        <v>0.0238220193661624</v>
       </c>
       <c r="F19" t="n">
-        <v>0.409230769230769</v>
+        <v>0.144923076923077</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>22.2532511978097</v>
+        <v>27.0116358658453</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0706382978723404</v>
+        <v>0.397872340425532</v>
       </c>
       <c r="K19" t="n">
-        <v>1360.18260944119</v>
+        <v>1399.33010741962</v>
       </c>
       <c r="L19" t="n">
-        <v>1391.70170412277</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1417.3340682403</v>
+        <v>1509.73901053658</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="B20" t="s">
-        <v>18</v>
-      </c>
       <c r="C20" t="n">
-        <v>0.324</v>
+        <v>0.232923076923077</v>
       </c>
       <c r="D20" t="n">
-        <v>0.418983050847458</v>
+        <v>0.232923076923077</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0183396576601775</v>
+        <v>0.023674179745061</v>
       </c>
       <c r="F20" t="n">
-        <v>0.176</v>
+        <v>0.267076923076923</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>27.4633812457221</v>
+        <v>25.6016427104723</v>
       </c>
       <c r="J20" t="n">
-        <v>0.525957446808511</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1476.8908765426</v>
+        <v>1271.43183373306</v>
       </c>
       <c r="L20" t="n">
-        <v>1522.85450560702</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1549.02431557902</v>
+        <v>1428.7838159466</v>
       </c>
     </row>
     <row r="21">
@@ -1482,81 +1416,75 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>0.102769230769231</v>
+        <v>0.290153846153846</v>
       </c>
       <c r="D21" t="n">
-        <v>0.102769230769231</v>
+        <v>0.421694915254237</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0180257097112059</v>
+        <v>0.0202464102275687</v>
       </c>
       <c r="F21" t="n">
-        <v>0.397230769230769</v>
+        <v>0.209846153846154</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>22.9075975359343</v>
+        <v>26.507871321013</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.52936170212766</v>
       </c>
       <c r="K21" t="n">
-        <v>1290.18965093973</v>
+        <v>1369.94965542054</v>
       </c>
       <c r="L21" t="n">
-        <v>1356.62262060248</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1350.64109828094</v>
+        <v>1493.34929174719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
       <c r="C22" t="n">
-        <v>0.237846153846154</v>
+        <v>0.300923076923077</v>
       </c>
       <c r="D22" t="n">
-        <v>0.257142857142857</v>
+        <v>0.300923076923077</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0179827413801329</v>
+        <v>0.0194556767083951</v>
       </c>
       <c r="F22" t="n">
-        <v>0.262153846153846</v>
+        <v>0.199076923076923</v>
       </c>
       <c r="G22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>28.6872005475702</v>
+        <v>27.9835728952772</v>
       </c>
       <c r="J22" t="n">
-        <v>0.310212765957447</v>
+        <v>0.353617021276596</v>
       </c>
       <c r="K22" t="n">
-        <v>1441.13315855315</v>
+        <v>1546.51037075601</v>
       </c>
       <c r="L22" t="n">
-        <v>1488.52578692821</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1523.77638795222</v>
+        <v>1532.76942657781</v>
       </c>
     </row>
     <row r="23">
@@ -1564,40 +1492,37 @@
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C23" t="n">
-        <v>0.232923076923077</v>
+        <v>0.324</v>
       </c>
       <c r="D23" t="n">
-        <v>0.232923076923077</v>
+        <v>0.418983050847458</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0176251926018</v>
+        <v>0.0189484781892471</v>
       </c>
       <c r="F23" t="n">
-        <v>0.267076923076923</v>
+        <v>0.176</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I23" t="n">
-        <v>25.6016427104723</v>
+        <v>27.4633812457221</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.525957446808511</v>
       </c>
       <c r="K23" t="n">
-        <v>1271.43183373306</v>
+        <v>1476.8908765426</v>
       </c>
       <c r="L23" t="n">
-        <v>1428.7838159466</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1297.62683315071</v>
+        <v>1522.85450560702</v>
       </c>
     </row>
     <row r="24">
@@ -1605,89 +1530,83 @@
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C24" t="n">
-        <v>0.315076923076923</v>
+        <v>0.303076923076923</v>
       </c>
       <c r="D24" t="n">
-        <v>0.436610169491525</v>
+        <v>0.303076923076923</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0167705348581255</v>
+        <v>0.0188831021345544</v>
       </c>
       <c r="F24" t="n">
-        <v>0.184923076923077</v>
+        <v>0.196923076923077</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I24" t="n">
-        <v>29.9219712525667</v>
+        <v>24.1232032854209</v>
       </c>
       <c r="J24" t="n">
-        <v>0.548085106382979</v>
+        <v>0.359574468085106</v>
       </c>
       <c r="K24" t="n">
-        <v>1403.82961319924</v>
+        <v>1461.298219278</v>
       </c>
       <c r="L24" t="n">
-        <v>1589.34409284569</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1434.23733844503</v>
+        <v>1468.58350050089</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C25" t="n">
-        <v>0.110153846153846</v>
+        <v>0.152615384615385</v>
       </c>
       <c r="D25" t="n">
-        <v>0.110153846153846</v>
+        <v>0.152615384615385</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0157179600045562</v>
+        <v>0.0185307881988714</v>
       </c>
       <c r="F25" t="n">
-        <v>0.389846153846154</v>
+        <v>0.347384615384615</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I25" t="n">
-        <v>22.715947980835</v>
+        <v>28.0355920602327</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0680851063829787</v>
+        <v>0.150212765957447</v>
       </c>
       <c r="K25" t="n">
-        <v>1285.3068804112</v>
+        <v>1261.46550968953</v>
       </c>
       <c r="L25" t="n">
-        <v>1366.85562344757</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1325.34561967385</v>
+        <v>1442.45437966006</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C26" t="n">
         <v>0.193230769230769</v>
@@ -1696,16 +1615,16 @@
         <v>0.193230769230769</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0150775660614802</v>
+        <v>0.0183615342352675</v>
       </c>
       <c r="F26" t="n">
         <v>0.306769230769231</v>
       </c>
       <c r="G26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I26" t="n">
         <v>24.4380561259411</v>
@@ -1718,9 +1637,6 @@
       </c>
       <c r="L26" t="n">
         <v>1455.31014095492</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1487.46712038075</v>
       </c>
     </row>
     <row r="27">
@@ -1728,122 +1644,113 @@
         <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C27" t="n">
-        <v>0.303076923076923</v>
+        <v>0.174461538461538</v>
       </c>
       <c r="D27" t="n">
-        <v>0.303076923076923</v>
+        <v>0.174461538461538</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0150743620337908</v>
+        <v>0.01760072617517</v>
       </c>
       <c r="F27" t="n">
-        <v>0.196923076923077</v>
+        <v>0.325538461538462</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I27" t="n">
-        <v>24.1232032854209</v>
+        <v>26.8665297741273</v>
       </c>
       <c r="J27" t="n">
-        <v>0.359574468085106</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1461.298219278</v>
+        <v>1309.11136166604</v>
       </c>
       <c r="L27" t="n">
-        <v>1468.58350050089</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1479.8328064448</v>
+        <v>1423.58983614881</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
-        <v>0.223384615384615</v>
+        <v>0.0907692307692308</v>
       </c>
       <c r="D28" t="n">
-        <v>0.223384615384615</v>
+        <v>0.112</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0141207600609243</v>
+        <v>0.0174357876630695</v>
       </c>
       <c r="F28" t="n">
-        <v>0.276615384615385</v>
+        <v>0.409230769230769</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I28" t="n">
-        <v>23.3511293634497</v>
+        <v>22.2532511978097</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0638297872340425</v>
+        <v>0.0706382978723404</v>
       </c>
       <c r="K28" t="n">
-        <v>1289.42556157946</v>
+        <v>1360.18260944119</v>
       </c>
       <c r="L28" t="n">
-        <v>1357.35954781588</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1333.56440357205</v>
+        <v>1391.70170412277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" t="s">
         <v>54</v>
       </c>
-      <c r="B29" t="s">
-        <v>14</v>
-      </c>
       <c r="C29" t="n">
-        <v>0.120615384615385</v>
+        <v>0.108615384615385</v>
       </c>
       <c r="D29" t="n">
-        <v>0.154</v>
+        <v>0.108615384615385</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0140555372160072</v>
+        <v>0.0169419837257347</v>
       </c>
       <c r="F29" t="n">
-        <v>0.379384615384615</v>
+        <v>0.391384615384615</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I29" t="n">
-        <v>23.854893908282</v>
+        <v>24.104038329911</v>
       </c>
       <c r="J29" t="n">
-        <v>0.188936170212766</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1276.18788638353</v>
+        <v>1271.86373863987</v>
       </c>
       <c r="L29" t="n">
-        <v>1456.32761576326</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1250.32966093779</v>
+        <v>1381.44373087077</v>
       </c>
     </row>
     <row r="30">
@@ -1851,40 +1758,37 @@
         <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C30" t="n">
-        <v>0.300923076923077</v>
+        <v>0.110153846153846</v>
       </c>
       <c r="D30" t="n">
-        <v>0.300923076923077</v>
+        <v>0.110153846153846</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0135797326705598</v>
+        <v>0.0154117091756262</v>
       </c>
       <c r="F30" t="n">
-        <v>0.199076923076923</v>
+        <v>0.389846153846154</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>27.9835728952772</v>
+        <v>22.715947980835</v>
       </c>
       <c r="J30" t="n">
-        <v>0.353617021276596</v>
+        <v>0.0680851063829787</v>
       </c>
       <c r="K30" t="n">
-        <v>1546.51037075601</v>
+        <v>1285.3068804112</v>
       </c>
       <c r="L30" t="n">
-        <v>1532.76942657781</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1552.1832670294</v>
+        <v>1366.85562344757</v>
       </c>
     </row>
     <row r="31">
@@ -1892,130 +1796,121 @@
         <v>56</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C31" t="n">
-        <v>0.268</v>
+        <v>0.237846153846154</v>
       </c>
       <c r="D31" t="n">
-        <v>0.28</v>
+        <v>0.257142857142857</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0129385415122724</v>
+        <v>0.0152763914480248</v>
       </c>
       <c r="F31" t="n">
-        <v>0.232</v>
+        <v>0.262153846153846</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I31" t="n">
-        <v>28.3422313483915</v>
+        <v>28.6872005475702</v>
       </c>
       <c r="J31" t="n">
-        <v>0.257021276595745</v>
+        <v>0.310212765957447</v>
       </c>
       <c r="K31" t="n">
-        <v>1304.75909230267</v>
+        <v>1441.13315855315</v>
       </c>
       <c r="L31" t="n">
-        <v>1408.17665780097</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1397.17371606791</v>
+        <v>1488.52578692821</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C32" t="n">
-        <v>0.152615384615385</v>
+        <v>0.102769230769231</v>
       </c>
       <c r="D32" t="n">
-        <v>0.152615384615385</v>
+        <v>0.102769230769231</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0108047695774349</v>
+        <v>0.0142109209008599</v>
       </c>
       <c r="F32" t="n">
-        <v>0.347384615384615</v>
+        <v>0.397230769230769</v>
       </c>
       <c r="G32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I32" t="n">
-        <v>28.0355920602327</v>
+        <v>22.9075975359343</v>
       </c>
       <c r="J32" t="n">
-        <v>0.150212765957447</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1261.46550968953</v>
+        <v>1290.18965093973</v>
       </c>
       <c r="L32" t="n">
-        <v>1442.45437966006</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1269.83671063539</v>
+        <v>1356.62262060248</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C33" t="n">
-        <v>0.108615384615385</v>
+        <v>0.167692307692308</v>
       </c>
       <c r="D33" t="n">
-        <v>0.108615384615385</v>
+        <v>0.178983050847458</v>
       </c>
       <c r="E33" t="n">
-        <v>0.010200831680769</v>
+        <v>0.0141019554428883</v>
       </c>
       <c r="F33" t="n">
-        <v>0.391384615384615</v>
+        <v>0.332307692307692</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I33" t="n">
-        <v>24.104038329911</v>
+        <v>25.8343600273785</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.22468085106383</v>
       </c>
       <c r="K33" t="n">
-        <v>1271.86373863987</v>
+        <v>1233.24340394809</v>
       </c>
       <c r="L33" t="n">
-        <v>1381.44373087077</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1247.78108600727</v>
+        <v>1392.98378888355</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C34" t="n">
         <v>0.101230769230769</v>
@@ -2024,16 +1919,16 @@
         <v>0.101230769230769</v>
       </c>
       <c r="E34" t="n">
-        <v>0.00997462324354466</v>
+        <v>0.0133128913186715</v>
       </c>
       <c r="F34" t="n">
         <v>0.398769230769231</v>
       </c>
       <c r="G34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I34" t="n">
         <v>18.4804928131417</v>
@@ -2047,426 +1942,393 @@
       <c r="L34" t="n">
         <v>1297.71670196998</v>
       </c>
-      <c r="M34" t="n">
-        <v>1236.88654449078</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C35" t="n">
-        <v>0.290153846153846</v>
+        <v>0.123384615384615</v>
       </c>
       <c r="D35" t="n">
-        <v>0.421694915254237</v>
+        <v>0.15952380952381</v>
       </c>
       <c r="E35" t="n">
-        <v>0.00938623199283935</v>
+        <v>0.0128579363009329</v>
       </c>
       <c r="F35" t="n">
-        <v>0.209846153846154</v>
+        <v>0.376615384615385</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>26.507871321013</v>
+        <v>25.3114305270363</v>
       </c>
       <c r="J35" t="n">
-        <v>0.52936170212766</v>
+        <v>0.176595744680851</v>
       </c>
       <c r="K35" t="n">
-        <v>1369.94965542054</v>
+        <v>1253.01824449709</v>
       </c>
       <c r="L35" t="n">
-        <v>1493.34929174719</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1358.41093950412</v>
+        <v>1379.37759673848</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C36" t="n">
-        <v>0.127692307692308</v>
+        <v>0.223384615384615</v>
       </c>
       <c r="D36" t="n">
-        <v>0.127692307692308</v>
+        <v>0.223384615384615</v>
       </c>
       <c r="E36" t="n">
-        <v>0.00879121317434824</v>
+        <v>0.0128538418047631</v>
       </c>
       <c r="F36" t="n">
-        <v>0.372307692307692</v>
+        <v>0.276615384615385</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>24.35318275154</v>
+        <v>23.3511293634497</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0553191489361702</v>
+        <v>0.0638297872340425</v>
       </c>
       <c r="K36" t="n">
-        <v>1297.46367045069</v>
+        <v>1289.42556157946</v>
       </c>
       <c r="L36" t="n">
-        <v>1345.30484900008</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1303.95636646834</v>
+        <v>1357.35954781588</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C37" t="n">
-        <v>0.137538461538462</v>
+        <v>0.268</v>
       </c>
       <c r="D37" t="n">
-        <v>0.137538461538462</v>
+        <v>0.28</v>
       </c>
       <c r="E37" t="n">
-        <v>0.00867614474903605</v>
+        <v>0.0100295008833894</v>
       </c>
       <c r="F37" t="n">
-        <v>0.362461538461539</v>
+        <v>0.232</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I37" t="n">
-        <v>30.0479123887748</v>
+        <v>28.3422313483915</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.257021276595745</v>
       </c>
       <c r="K37" t="n">
-        <v>1233.46610879806</v>
+        <v>1304.75909230267</v>
       </c>
       <c r="L37" t="n">
-        <v>1321.78410437128</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1334.00200838412</v>
+        <v>1408.17665780097</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C38" t="n">
-        <v>0.072</v>
+        <v>0.127692307692308</v>
       </c>
       <c r="D38" t="n">
-        <v>0.072</v>
+        <v>0.127692307692308</v>
       </c>
       <c r="E38" t="n">
-        <v>0.00822186266611494</v>
+        <v>0.0099311375374492</v>
       </c>
       <c r="F38" t="n">
-        <v>0.428</v>
+        <v>0.372307692307692</v>
       </c>
       <c r="G38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I38" t="n">
-        <v>23.27446954141</v>
+        <v>24.35318275154</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.0553191489361702</v>
       </c>
       <c r="K38" t="n">
-        <v>1296.01417059747</v>
+        <v>1297.46367045069</v>
       </c>
       <c r="L38" t="n">
-        <v>1319.62250853855</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1292.79386419316</v>
+        <v>1345.30484900008</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0907692307692308</v>
+        <v>0.072</v>
       </c>
       <c r="D39" t="n">
-        <v>0.185</v>
+        <v>0.072</v>
       </c>
       <c r="E39" t="n">
-        <v>0.00805968966791138</v>
+        <v>0.0090147402826405</v>
       </c>
       <c r="F39" t="n">
-        <v>0.409230769230769</v>
+        <v>0.428</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>30.1984941820671</v>
+        <v>23.27446954141</v>
       </c>
       <c r="J39" t="n">
-        <v>0.102978723404255</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1216.33471054527</v>
+        <v>1296.01417059747</v>
       </c>
       <c r="L39" t="n">
-        <v>1371.14683192814</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1276.89210167229</v>
+        <v>1319.62250853855</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="C40" t="n">
-        <v>0.167692307692308</v>
+        <v>0.0836923076923077</v>
       </c>
       <c r="D40" t="n">
-        <v>0.178983050847458</v>
+        <v>0.265084745762712</v>
       </c>
       <c r="E40" t="n">
-        <v>0.00793854531027747</v>
+        <v>0.00894900652277903</v>
       </c>
       <c r="F40" t="n">
-        <v>0.332307692307692</v>
+        <v>0.416307692307692</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I40" t="n">
-        <v>25.8343600273785</v>
+        <v>28.4791238877481</v>
       </c>
       <c r="J40" t="n">
-        <v>0.22468085106383</v>
+        <v>0.332765957446809</v>
       </c>
       <c r="K40" t="n">
-        <v>1233.24340394809</v>
+        <v>1352.93310103119</v>
       </c>
       <c r="L40" t="n">
-        <v>1392.98378888355</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1225.58986454127</v>
+        <v>1417.22839263661</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0836923076923077</v>
+        <v>0.0593846153846154</v>
       </c>
       <c r="D41" t="n">
-        <v>0.265084745762712</v>
+        <v>0.0593846153846154</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00764642510791657</v>
+        <v>0.00868776285425909</v>
       </c>
       <c r="F41" t="n">
-        <v>0.416307692307692</v>
+        <v>0.440615384615385</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>28.4791238877481</v>
+        <v>23.5181382614647</v>
       </c>
       <c r="J41" t="n">
-        <v>0.332765957446809</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1352.93310103119</v>
+        <v>1271.43183373306</v>
       </c>
       <c r="L41" t="n">
-        <v>1417.22839263661</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1384.11300378991</v>
+        <v>1312.88083316645</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0593846153846154</v>
+        <v>0.0907692307692308</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0593846153846154</v>
+        <v>0.185</v>
       </c>
       <c r="E42" t="n">
-        <v>0.00680304964067933</v>
+        <v>0.00788880967549245</v>
       </c>
       <c r="F42" t="n">
-        <v>0.440615384615385</v>
+        <v>0.409230769230769</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I42" t="n">
-        <v>23.5181382614647</v>
+        <v>30.1984941820671</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.102978723404255</v>
       </c>
       <c r="K42" t="n">
-        <v>1271.43183373306</v>
+        <v>1216.33471054527</v>
       </c>
       <c r="L42" t="n">
-        <v>1312.88083316645</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1251.23306682443</v>
+        <v>1371.14683192814</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0818461538461538</v>
+        <v>0.0781538461538462</v>
       </c>
       <c r="D43" t="n">
-        <v>0.117627118644068</v>
+        <v>0.0781538461538462</v>
       </c>
       <c r="E43" t="n">
-        <v>0.00671482671032834</v>
+        <v>0.00662926002462249</v>
       </c>
       <c r="F43" t="n">
-        <v>0.418153846153846</v>
+        <v>0.421846153846154</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I43" t="n">
-        <v>25.1006160164271</v>
+        <v>24.2956878850103</v>
       </c>
       <c r="J43" t="n">
-        <v>0.147659574468085</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1322.73795047265</v>
+        <v>1237.541613594</v>
       </c>
       <c r="L43" t="n">
-        <v>1329.37465579372</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1337.60147513046</v>
+        <v>1287.98725376794</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C44" t="n">
-        <v>0.092</v>
+        <v>0.0818461538461538</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0959322033898305</v>
+        <v>0.117627118644068</v>
       </c>
       <c r="E44" t="n">
-        <v>0.00603536157835318</v>
+        <v>0.0065899075249384</v>
       </c>
       <c r="F44" t="n">
-        <v>0.408</v>
+        <v>0.418153846153846</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I44" t="n">
-        <v>26.1519507186858</v>
+        <v>25.1006160164271</v>
       </c>
       <c r="J44" t="n">
-        <v>0.108125</v>
+        <v>0.147659574468085</v>
       </c>
       <c r="K44" t="n">
-        <v>1333.9801969242</v>
+        <v>1322.73795047265</v>
       </c>
       <c r="L44" t="n">
-        <v>1324.51494392349</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1349.49303069682</v>
+        <v>1329.37465579372</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>70</v>
+      </c>
+      <c r="B45" t="s">
         <v>71</v>
-      </c>
-      <c r="B45" t="s">
-        <v>72</v>
       </c>
       <c r="C45" t="n">
         <v>0.0526153846153846</v>
@@ -2475,16 +2337,16 @@
         <v>0.0526153846153846</v>
       </c>
       <c r="E45" t="n">
-        <v>0.00594444095388648</v>
+        <v>0.00619227210207183</v>
       </c>
       <c r="F45" t="n">
         <v>0.447384615384615</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I45" t="n">
         <v>22.4531143052704</v>
@@ -2498,49 +2360,43 @@
       <c r="L45" t="n">
         <v>1265.99555607072</v>
       </c>
-      <c r="M45" t="n">
-        <v>1244.60469124343</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" t="s">
         <v>73</v>
       </c>
-      <c r="B46" t="s">
-        <v>40</v>
-      </c>
       <c r="C46" t="n">
-        <v>0.123384615384615</v>
+        <v>0.072</v>
       </c>
       <c r="D46" t="n">
-        <v>0.15952380952381</v>
+        <v>0.072</v>
       </c>
       <c r="E46" t="n">
-        <v>0.00536269728196657</v>
+        <v>0.00560391290827677</v>
       </c>
       <c r="F46" t="n">
-        <v>0.376615384615385</v>
+        <v>0.428</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I46" t="n">
-        <v>25.3114305270363</v>
+        <v>21.2183436002738</v>
       </c>
       <c r="J46" t="n">
-        <v>0.176595744680851</v>
+        <v>0.0617021276595745</v>
       </c>
       <c r="K46" t="n">
-        <v>1253.01824449709</v>
+        <v>1293.64467355037</v>
       </c>
       <c r="L46" t="n">
-        <v>1379.37759673848</v>
-      </c>
-      <c r="M46" t="n">
-        <v>1191.42221103118</v>
+        <v>1258.33158349241</v>
       </c>
     </row>
     <row r="47">
@@ -2548,40 +2404,37 @@
         <v>74</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0858461538461538</v>
+        <v>0.092</v>
       </c>
       <c r="D47" t="n">
-        <v>0.205714285714286</v>
+        <v>0.0959322033898305</v>
       </c>
       <c r="E47" t="n">
-        <v>0.00510462257492464</v>
+        <v>0.00557860994297937</v>
       </c>
       <c r="F47" t="n">
-        <v>0.414153846153846</v>
+        <v>0.408</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I47" t="n">
-        <v>27.0116358658453</v>
+        <v>26.1519507186858</v>
       </c>
       <c r="J47" t="n">
-        <v>0.160851063829787</v>
+        <v>0.108125</v>
       </c>
       <c r="K47" t="n">
-        <v>1276.11681483465</v>
+        <v>1333.9801969242</v>
       </c>
       <c r="L47" t="n">
-        <v>1303.22525135947</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1307.75172445489</v>
+        <v>1324.51494392349</v>
       </c>
     </row>
     <row r="48">
@@ -2589,163 +2442,151 @@
         <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="C48" t="n">
-        <v>0.072</v>
+        <v>0.0636923076923077</v>
       </c>
       <c r="D48" t="n">
-        <v>0.072</v>
+        <v>0.127796610169492</v>
       </c>
       <c r="E48" t="n">
-        <v>0.00468242991500202</v>
+        <v>0.0051444944232178</v>
       </c>
       <c r="F48" t="n">
-        <v>0.428</v>
+        <v>0.436307692307692</v>
       </c>
       <c r="G48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I48" t="n">
-        <v>21.2183436002738</v>
+        <v>25.9575633127995</v>
       </c>
       <c r="J48" t="n">
-        <v>0.0617021276595745</v>
+        <v>0.160425531914894</v>
       </c>
       <c r="K48" t="n">
-        <v>1293.64467355037</v>
+        <v>1208.84200168761</v>
       </c>
       <c r="L48" t="n">
-        <v>1258.33158349241</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1253.94328448433</v>
+        <v>1289.3075987102</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0812307692307692</v>
+        <v>0.0590769230769231</v>
       </c>
       <c r="D49" t="n">
-        <v>0.211525423728814</v>
+        <v>0.0590769230769231</v>
       </c>
       <c r="E49" t="n">
-        <v>0.00466024168936945</v>
+        <v>0.00495971493337759</v>
       </c>
       <c r="F49" t="n">
-        <v>0.418769230769231</v>
+        <v>0.440923076923077</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I49" t="n">
-        <v>28.7912388774812</v>
+        <v>21.2511978097194</v>
       </c>
       <c r="J49" t="n">
-        <v>0.265531914893617</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1334.87466385146</v>
+        <v>1271.43183373306</v>
       </c>
       <c r="L49" t="n">
-        <v>1324.14959874607</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1383.05526180202</v>
+        <v>1236.70132533885</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0590769230769231</v>
+        <v>0.137538461538462</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0590769230769231</v>
+        <v>0.137538461538462</v>
       </c>
       <c r="E50" t="n">
-        <v>0.00452710281408768</v>
+        <v>0.00495860293555037</v>
       </c>
       <c r="F50" t="n">
-        <v>0.440923076923077</v>
+        <v>0.362461538461539</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I50" t="n">
-        <v>21.2511978097194</v>
+        <v>30.0479123887748</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1271.43183373306</v>
+        <v>1233.46610879806</v>
       </c>
       <c r="L50" t="n">
-        <v>1236.70132533885</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1236.83913718219</v>
+        <v>1321.78410437128</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B51" t="s">
         <v>79</v>
       </c>
-      <c r="B51" t="s">
-        <v>14</v>
-      </c>
       <c r="C51" t="n">
-        <v>0.0781538461538462</v>
+        <v>0.0341538461538462</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0781538461538462</v>
+        <v>0.0852380952380952</v>
       </c>
       <c r="E51" t="n">
-        <v>0.00451396603131073</v>
+        <v>0.00453753150780942</v>
       </c>
       <c r="F51" t="n">
-        <v>0.421846153846154</v>
+        <v>0.465846153846154</v>
       </c>
       <c r="G51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I51" t="n">
-        <v>24.2956878850103</v>
+        <v>23.8302532511978</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>0.0685106382978723</v>
       </c>
       <c r="K51" t="n">
-        <v>1237.541613594</v>
+        <v>1271.71262767943</v>
       </c>
       <c r="L51" t="n">
-        <v>1287.98725376794</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1196.07122470498</v>
+        <v>1262.11272166664</v>
       </c>
     </row>
     <row r="52">
@@ -2753,48 +2594,45 @@
         <v>80</v>
       </c>
       <c r="B52" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0341538461538462</v>
+        <v>0.0858461538461538</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0852380952380952</v>
+        <v>0.205714285714286</v>
       </c>
       <c r="E52" t="n">
-        <v>0.00439497148078017</v>
+        <v>0.00443897615876861</v>
       </c>
       <c r="F52" t="n">
-        <v>0.465846153846154</v>
+        <v>0.414153846153846</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I52" t="n">
-        <v>23.8302532511978</v>
+        <v>27.0116358658453</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0685106382978723</v>
+        <v>0.160851063829787</v>
       </c>
       <c r="K52" t="n">
-        <v>1271.71262767943</v>
+        <v>1276.11681483465</v>
       </c>
       <c r="L52" t="n">
-        <v>1262.11272166664</v>
-      </c>
-      <c r="M52" t="n">
-        <v>1259.16006980673</v>
+        <v>1303.22525135947</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" t="n">
         <v>0.0427692307692308</v>
@@ -2803,16 +2641,16 @@
         <v>0.0427692307692308</v>
       </c>
       <c r="E53" t="n">
-        <v>0.00416529934148609</v>
+        <v>0.00395637805364726</v>
       </c>
       <c r="F53" t="n">
         <v>0.457230769230769</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I53" t="n">
         <v>22.4531143052704</v>
@@ -2826,180 +2664,165 @@
       <c r="L53" t="n">
         <v>1229.72889354893</v>
       </c>
-      <c r="M53" t="n">
-        <v>1255.44233236977</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0636923076923077</v>
+        <v>0.068</v>
       </c>
       <c r="D54" t="n">
-        <v>0.127796610169492</v>
+        <v>0.068</v>
       </c>
       <c r="E54" t="n">
-        <v>0.00377244072350651</v>
+        <v>0.00352542028505914</v>
       </c>
       <c r="F54" t="n">
-        <v>0.436307692307692</v>
+        <v>0.432</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I54" t="n">
-        <v>25.9575633127995</v>
+        <v>22.7679671457906</v>
       </c>
       <c r="J54" t="n">
-        <v>0.160425531914894</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1208.84200168761</v>
+        <v>1278.48462181737</v>
       </c>
       <c r="L54" t="n">
-        <v>1289.3075987102</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1192.38473917297</v>
+        <v>1223.13316781123</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="C55" t="n">
-        <v>0.068</v>
+        <v>0.0812307692307692</v>
       </c>
       <c r="D55" t="n">
-        <v>0.068</v>
+        <v>0.211525423728814</v>
       </c>
       <c r="E55" t="n">
-        <v>0.00344397301423275</v>
+        <v>0.00352185272203973</v>
       </c>
       <c r="F55" t="n">
-        <v>0.432</v>
+        <v>0.418769230769231</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I55" t="n">
-        <v>22.7679671457906</v>
+        <v>28.7912388774812</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>0.265531914893617</v>
       </c>
       <c r="K55" t="n">
-        <v>1278.48462181737</v>
+        <v>1334.87466385146</v>
       </c>
       <c r="L55" t="n">
-        <v>1223.13316781123</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1244.27137065237</v>
+        <v>1324.14959874607</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0547692307692308</v>
+        <v>0.0541538461538462</v>
       </c>
       <c r="D56" t="n">
-        <v>0.107457627118644</v>
+        <v>0.0541538461538462</v>
       </c>
       <c r="E56" t="n">
-        <v>0.0031359098732914</v>
+        <v>0.00341678786632834</v>
       </c>
       <c r="F56" t="n">
-        <v>0.445230769230769</v>
+        <v>0.445846153846154</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I56" t="n">
-        <v>24.7857631759069</v>
+        <v>21.4784394250513</v>
       </c>
       <c r="J56" t="n">
-        <v>0.134893617021277</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1290.69472971623</v>
+        <v>1255.30433525932</v>
       </c>
       <c r="L56" t="n">
-        <v>1237.60403450714</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1284.27084186339</v>
+        <v>1200.84120910091</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0541538461538462</v>
+        <v>0.0547692307692308</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0541538461538462</v>
+        <v>0.107457627118644</v>
       </c>
       <c r="E57" t="n">
-        <v>0.00291184494567395</v>
+        <v>0.00278437227096317</v>
       </c>
       <c r="F57" t="n">
-        <v>0.445846153846154</v>
+        <v>0.445230769230769</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I57" t="n">
-        <v>21.4784394250513</v>
+        <v>24.7857631759069</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>0.134893617021277</v>
       </c>
       <c r="K57" t="n">
-        <v>1255.30433525932</v>
+        <v>1290.69472971623</v>
       </c>
       <c r="L57" t="n">
-        <v>1200.84120910091</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1199.09942202136</v>
+        <v>1237.60403450714</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C58" t="n">
         <v>0.00892307692307692</v>
@@ -3008,16 +2831,16 @@
         <v>0.00892307692307692</v>
       </c>
       <c r="E58" t="n">
-        <v>0.00271800824952925</v>
+        <v>0.00262143380684941</v>
       </c>
       <c r="F58" t="n">
         <v>0.491076923076923</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I58" t="n">
         <v>21.7029431895962</v>
@@ -3031,16 +2854,13 @@
       <c r="L58" t="n">
         <v>1173.36975081209</v>
       </c>
-      <c r="M58" t="n">
-        <v>1196.032227627</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59" t="s">
         <v>89</v>
-      </c>
-      <c r="B59" t="s">
-        <v>90</v>
       </c>
       <c r="C59" t="n">
         <v>0.0415384615384615</v>
@@ -3049,16 +2869,16 @@
         <v>0.0415384615384615</v>
       </c>
       <c r="E59" t="n">
-        <v>0.00135046845007331</v>
+        <v>0.00156439113772288</v>
       </c>
       <c r="F59" t="n">
         <v>0.458461538461538</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I59" t="n">
         <v>24.082135523614</v>
@@ -3072,16 +2892,13 @@
       <c r="L59" t="n">
         <v>1142.18749486996</v>
       </c>
-      <c r="M59" t="n">
-        <v>1128.82147664918</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C60" t="n">
         <v>0.0338461538461538</v>
@@ -3090,16 +2907,16 @@
         <v>0.149830508474576</v>
       </c>
       <c r="E60" t="n">
-        <v>0.00113105516462924</v>
+        <v>0.00131118638407599</v>
       </c>
       <c r="F60" t="n">
         <v>0.466153846153846</v>
       </c>
       <c r="G60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I60" t="n">
         <v>27.6577686516085</v>
@@ -3113,16 +2930,13 @@
       <c r="L60" t="n">
         <v>1183.87064889063</v>
       </c>
-      <c r="M60" t="n">
-        <v>1165.54556602821</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" t="n">
         <v>0.0230769230769231</v>
@@ -3131,16 +2945,16 @@
         <v>0.0254237288135593</v>
       </c>
       <c r="E61" t="n">
-        <v>0.00060244803618656</v>
+        <v>0.000681712854030749</v>
       </c>
       <c r="F61" t="n">
         <v>0.476923076923077</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I61" t="n">
         <v>25.9739904175222</v>
@@ -3154,172 +2968,157 @@
       <c r="L61" t="n">
         <v>1101.74814756447</v>
       </c>
-      <c r="M61" t="n">
-        <v>1159.90266034152</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C62" t="n">
-        <v>0.064</v>
+        <v>0.00184615384615385</v>
       </c>
       <c r="D62" t="n">
-        <v>0.064</v>
+        <v>0.0122033898305085</v>
       </c>
       <c r="E62" t="n">
-        <v>0.000466290039140035</v>
+        <v>0.000524500911109105</v>
       </c>
       <c r="F62" t="n">
-        <v>0.436</v>
+        <v>0.498153846153846</v>
       </c>
       <c r="G62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I62" t="n">
-        <v>25.5277207392197</v>
+        <v>28.3066392881588</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0480851063829787</v>
+        <v>0.0153191489361702</v>
       </c>
       <c r="K62" t="n">
-        <v>1159.19338859055</v>
+        <v>1212.58658010767</v>
       </c>
       <c r="L62" t="n">
-        <v>1045.18429098974</v>
-      </c>
-      <c r="M62" t="n">
-        <v>1073.87843707507</v>
+        <v>1092.44951675035</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="C63" t="n">
-        <v>0.016</v>
+        <v>0.064</v>
       </c>
       <c r="D63" t="n">
-        <v>0.016</v>
+        <v>0.064</v>
       </c>
       <c r="E63" t="n">
-        <v>0.000459733927535229</v>
+        <v>0.00048366662489168</v>
       </c>
       <c r="F63" t="n">
-        <v>0.484</v>
+        <v>0.436</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I63" t="n">
-        <v>27.4414784394251</v>
+        <v>25.5277207392197</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>0.0480851063829787</v>
       </c>
       <c r="K63" t="n">
-        <v>1239.68841940139</v>
+        <v>1159.19338859055</v>
       </c>
       <c r="L63" t="n">
-        <v>1076.74837439515</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1148.61303282245</v>
+        <v>1045.18429098974</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00184615384615385</v>
+        <v>0.0883076923076923</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0122033898305085</v>
+        <v>0.0883076923076923</v>
       </c>
       <c r="E64" t="n">
-        <v>0.000440552963971332</v>
+        <v>0.000466649368770981</v>
       </c>
       <c r="F64" t="n">
-        <v>0.498153846153846</v>
+        <v>0.411692307692308</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I64" t="n">
-        <v>28.3066392881588</v>
+        <v>25.533196440794</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0153191489361702</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1212.58658010767</v>
+        <v>1179.02765080658</v>
       </c>
       <c r="L64" t="n">
-        <v>1092.44951675035</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1114.14558037925</v>
+        <v>1042.56692483525</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0883076923076923</v>
+        <v>0.016</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0883076923076923</v>
+        <v>0.016</v>
       </c>
       <c r="E65" t="n">
-        <v>0.000376115132786825</v>
+        <v>0.000462176126630382</v>
       </c>
       <c r="F65" t="n">
-        <v>0.411692307692308</v>
+        <v>0.484</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I65" t="n">
-        <v>25.533196440794</v>
+        <v>27.4414784394251</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1179.02765080658</v>
+        <v>1239.68841940139</v>
       </c>
       <c r="L65" t="n">
-        <v>1042.56692483525</v>
-      </c>
-      <c r="M65" t="n">
-        <v>1061.03839181088</v>
+        <v>1076.74837439515</v>
       </c>
     </row>
   </sheetData>
@@ -3338,59 +3137,50 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" t="s">
         <v>97</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>98</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>99</v>
-      </c>
-      <c r="E1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2" t="n">
-        <v>27.2635181382615</v>
+        <v>25.09787816564</v>
       </c>
       <c r="C2" t="n">
-        <v>0.226382978723404</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1326.28779016586</v>
+        <v>1284.62144934536</v>
       </c>
       <c r="E2" t="n">
-        <v>1599.42130718551</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1560.61026383801</v>
+        <v>1694.59171167798</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>25.7302782395185</v>
+        <v>25.7646534771791</v>
       </c>
       <c r="C3" t="n">
-        <v>0.159203605200946</v>
+        <v>0.162796985815603</v>
       </c>
       <c r="D3" t="n">
-        <v>1313.93245922077</v>
+        <v>1314.59382970999</v>
       </c>
       <c r="E3" t="n">
-        <v>1375.25812893685</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1332.022265362</v>
+        <v>1373.74748759569</v>
       </c>
     </row>
   </sheetData>
@@ -3406,18 +3196,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B2" t="n">
-        <v>0.88921275071413</v>
+        <v>0.883877814368281</v>
       </c>
     </row>
   </sheetData>
